--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_389_R42.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_389_R42.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5339</v>
+        <v>6.433</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0608</v>
+        <v>6.9922</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5269</v>
+        <v>-0.5592</v>
       </c>
       <c r="G2" t="n">
         <v>1.5913</v>
@@ -610,13 +610,13 @@
         <v>1.3648</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4448</v>
+        <v>1.3439</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7658</v>
+        <v>1.6972</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.321</v>
+        <v>-0.3533</v>
       </c>
       <c r="V2" t="n">
         <v>3.2703</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0144</v>
+        <v>5.6178</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0653</v>
+        <v>5.6041</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0509</v>
+        <v>0.0137</v>
       </c>
       <c r="G3" t="n">
         <v>5.5748</v>
@@ -688,13 +688,13 @@
         <v>0.6824</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8788</v>
+        <v>-0.2754</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5028</v>
+        <v>0.036</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.376</v>
+        <v>-0.3114</v>
       </c>
       <c r="V3" t="n">
         <v>0.7734</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.014</v>
+        <v>4.515</v>
       </c>
       <c r="E4" t="n">
-        <v>2.27</v>
+        <v>2.6741</v>
       </c>
       <c r="F4" t="n">
-        <v>1.744</v>
+        <v>1.841</v>
       </c>
       <c r="G4" t="n">
         <v>2.3232</v>
@@ -766,13 +766,13 @@
         <v>2.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9865</v>
+        <v>1.4875</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0059</v>
+        <v>1.4099</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0193</v>
+        <v>0.0776</v>
       </c>
       <c r="V4" t="n">
         <v>0.9318</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1054</v>
+        <v>2.8255</v>
       </c>
       <c r="E5" t="n">
-        <v>3.945</v>
+        <v>4.6005</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8397</v>
+        <v>-1.775</v>
       </c>
       <c r="G5" t="n">
         <v>2.3263</v>
@@ -844,13 +844,13 @@
         <v>1.3648</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4957</v>
+        <v>0.2245</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2633</v>
+        <v>0.3922</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2324</v>
+        <v>-0.1677</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0901</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1615</v>
+        <v>0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9096</v>
+        <v>0.9757</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7481</v>
+        <v>-0.7157</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0989</v>
@@ -922,13 +922,13 @@
         <v>0.6824</v>
       </c>
       <c r="S6" t="n">
-        <v>1.578</v>
+        <v>0.6765</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7121</v>
+        <v>0.7782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1341</v>
+        <v>-0.1018</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8325</v>
+        <v>-0.6185</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3418</v>
+        <v>0.2463</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5093</v>
+        <v>-0.8648</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3545</v>
@@ -1000,13 +1000,13 @@
         <v>0.6824</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7321</v>
+        <v>1.2811</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7003</v>
+        <v>0.6047</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0319</v>
+        <v>0.6763</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0901</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4818</v>
+        <v>-1.0009</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2702</v>
+        <v>-0.8539</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2116</v>
+        <v>-0.147</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1688</v>
@@ -1078,13 +1078,13 @@
         <v>0.4549</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5277</v>
+        <v>1.0087</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4846</v>
+        <v>0.901</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0431</v>
+        <v>0.1077</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1583</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3568</v>
+        <v>-1.5702</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5414</v>
+        <v>-0.7871</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8154</v>
+        <v>-0.7831</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0487</v>
@@ -1156,13 +1156,13 @@
         <v>1.8198</v>
       </c>
       <c r="S9" t="n">
-        <v>0.237</v>
+        <v>1.0236</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4551</v>
+        <v>1.2093</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2181</v>
+        <v>-0.1857</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0901</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0697</v>
+        <v>-2.0119</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.798</v>
+        <v>-2.8372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8253</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0505</v>
@@ -1234,13 +1234,13 @@
         <v>1.3648</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2467</v>
+        <v>0.8111</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2633</v>
+        <v>0.6975</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0167</v>
+        <v>0.1136</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9605</v>
+        <v>-2.2203</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8135</v>
+        <v>-4.0087</v>
       </c>
       <c r="F11" t="n">
-        <v>1.853</v>
+        <v>1.7884</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5947</v>
@@ -1312,13 +1312,13 @@
         <v>2.0473</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1364</v>
+        <v>1.8766</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>1.5535</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3877</v>
+        <v>0.3231</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.7929</v>
+        <v>12.2295</v>
       </c>
       <c r="E12" t="n">
-        <v>11.1694</v>
+        <v>12.606</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3766000000000005</v>
+        <v>-0.3764000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>3.499500000000001</v>
@@ -1390,13 +1390,13 @@
         <v>12.5109</v>
       </c>
       <c r="S12" t="n">
-        <v>8.021299999999998</v>
+        <v>9.4581</v>
       </c>
       <c r="T12" t="n">
-        <v>7.843100000000001</v>
+        <v>9.279499999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1785</v>
+        <v>0.1784</v>
       </c>
       <c r="V12" t="n">
         <v>1.5469</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3419</v>
+        <v>1.8998</v>
       </c>
       <c r="E13" t="n">
-        <v>1.234</v>
+        <v>1.7009</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1079</v>
+        <v>0.1989</v>
       </c>
       <c r="G13" t="n">
         <v>0.7385</v>
@@ -1468,13 +1468,13 @@
         <v>1.5923</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.989</v>
+        <v>-0.431</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5626</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4264</v>
+        <v>-0.3354</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9771</v>
+        <v>1.1393</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0595</v>
+        <v>-0.1763</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0366</v>
+        <v>1.3156</v>
       </c>
       <c r="G14" t="n">
         <v>2.1087</v>
@@ -1546,13 +1546,13 @@
         <v>1.8198</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.6256</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2153</v>
+        <v>-0.3321</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5725</v>
+        <v>-0.2935</v>
       </c>
       <c r="V14" t="n">
         <v>1.2485</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5137</v>
+        <v>0.5784</v>
       </c>
       <c r="E15" t="n">
         <v>0.6114000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.033</v>
       </c>
       <c r="G15" t="n">
         <v>0.327</v>
@@ -1624,13 +1624,13 @@
         <v>0.6824</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4957</v>
+        <v>-0.431</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0718</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4238</v>
+        <v>-0.3592</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6613</v>
+        <v>-0.042</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7616</v>
+        <v>1.3387</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4229</v>
+        <v>-1.3807</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3091</v>
+        <v>-1.4847</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0028</v>
+        <v>-0.0491</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6937</v>
+        <v>-1.4355</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9723</v>
+        <v>1.0692</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8978</v>
+        <v>0.2415</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0745</v>
+        <v>0.8277</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6632</v>
+        <v>-2.5539</v>
       </c>
       <c r="N16" t="n">
-        <v>0.105</v>
+        <v>-0.2907</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7682</v>
+        <v>-2.2632</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0167</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5628</v>
+        <v>0.2695</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5795</v>
+        <v>-0.1916</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8635</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.786</v>
+        <v>-0.6744</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8081</v>
+        <v>1.5282</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.594</v>
+        <v>-2.2026</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3768</v>
+        <v>0.3091</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9164</v>
+        <v>2.0028</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.2933</v>
+        <v>-1.6937</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1551</v>
+        <v>1.9723</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3408</v>
+        <v>1.8978</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1857</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5319</v>
+        <v>-1.6632</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5757</v>
+        <v>0.105</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1076</v>
+        <v>-1.7682</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2747</v>
+        <v>0.9099</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2747</v>
+        <v>0.9099</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5938</v>
+        <v>-0.0299</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5629</v>
+        <v>0.3293</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1567</v>
+        <v>-0.3592</v>
       </c>
       <c r="V17" t="n">
+        <v>-1.8635</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.7734</v>
+      </c>
+      <c r="X17" t="n">
         <v>-1.0901</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.0901</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-2.1802</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0537</v>
+        <v>-0.8057</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6383</v>
+        <v>1.2244</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.692</v>
+        <v>-2.0301</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4847</v>
+        <v>-1.3768</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0491</v>
+        <v>2.9164</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4355</v>
+        <v>-4.2933</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0692</v>
+        <v>0.1551</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2415</v>
+        <v>2.3408</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8277</v>
+        <v>-2.1857</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5539</v>
+        <v>-1.5319</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2907</v>
+        <v>0.5757</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2632</v>
+        <v>-2.1076</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3648</v>
+        <v>2.2747</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3648</v>
+        <v>2.2747</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9339</v>
+        <v>-0.6136</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.431</v>
+        <v>-0.0208</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5029</v>
+        <v>-0.5928</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3803</v>
+        <v>-1.2827</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1414</v>
+        <v>-0.6036</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5217</v>
+        <v>-0.6791</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8942</v>
+        <v>-0.0197</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4977</v>
+        <v>3.5071</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3965</v>
+        <v>-3.5268</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8597</v>
+        <v>1.0178</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4831</v>
+        <v>3.1209</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3766</v>
+        <v>-2.1031</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7539</v>
+        <v>-1.0375</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9808</v>
+        <v>0.3863</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7731</v>
+        <v>-1.4237</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9099</v>
+        <v>2.2747</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2586</v>
+        <v>-1.2631</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4191</v>
+        <v>-0.4368</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6778</v>
+        <v>-0.8263</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4113</v>
+        <v>-1.6646</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1107</v>
+        <v>-2.4609</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6993</v>
+        <v>0.7963</v>
       </c>
       <c r="G20" t="n">
         <v>-1.045</v>
@@ -2014,13 +2014,13 @@
         <v>1.1374</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3663</v>
+        <v>-0.6196</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2036</v>
+        <v>-0.1466</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5699</v>
+        <v>-0.473</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5494</v>
+        <v>-1.7233</v>
       </c>
       <c r="E21" t="n">
-        <v>0.197</v>
+        <v>0.0247</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7464</v>
+        <v>-1.748</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2927</v>
+        <v>-0.8942</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0544</v>
+        <v>-0.4977</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2383</v>
+        <v>-0.3965</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5886</v>
+        <v>0.8597</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0075</v>
+        <v>0.4831</v>
       </c>
       <c r="L21" t="n">
-        <v>0.596</v>
+        <v>0.3766</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8812</v>
+        <v>-1.7539</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0469</v>
+        <v>-0.9808</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8343</v>
+        <v>-0.7731</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6824</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5923</v>
+        <v>0.9099</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7326</v>
+        <v>-0.6016</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6347</v>
+        <v>0.3024</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3674</v>
+        <v>-0.904</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2485</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2562</v>
+        <v>-1.7445</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.304</v>
+        <v>-0.5034</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-1.2412</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0197</v>
+        <v>-0.2927</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5071</v>
+        <v>-0.0544</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5268</v>
+        <v>-0.2383</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0178</v>
+        <v>0.5886</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1209</v>
+        <v>-0.0075</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1031</v>
+        <v>0.596</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0375</v>
+        <v>-0.8812</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3863</v>
+        <v>-0.0469</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4237</v>
+        <v>-0.8343</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.2747</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2747</v>
+        <v>1.5923</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2365</v>
+        <v>-0.9278</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1372</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0993</v>
+        <v>-0.8621</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0901</v>
+        <v>1.2485</v>
       </c>
       <c r="X22" t="n">
         <v>-1.0901</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5275</v>
+        <v>-4.1384</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.541</v>
+        <v>-2.3076</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9865</v>
+        <v>-1.8309</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8697</v>
@@ -2248,13 +2248,13 @@
         <v>0.2275</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6106</v>
+        <v>-0.2215</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1437</v>
+        <v>0.0898</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4669</v>
+        <v>-0.3113</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.793</v>
+        <v>-8.458100000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3766000000000003</v>
+        <v>0.3765000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.1694</v>
+        <v>-8.8348</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4995</v>
@@ -2305,7 +2305,7 @@
         <v>13.6991</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.6951</v>
+        <v>-4.695100000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-12.5034</v>
@@ -2326,13 +2326,13 @@
         <v>14.7857</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.0215</v>
+        <v>-5.686900000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1785000000000002</v>
+        <v>-0.1785</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.843100000000001</v>
+        <v>-5.5084</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5468</v>
